--- a/backend/reports/azure_cost_report.xlsx
+++ b/backend/reports/azure_cost_report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>245.616</v>
+        <v>246.288</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>141.702252</v>
+        <v>141.999252</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121.160656186</v>
+        <v>121.326656186</v>
       </c>
     </row>
     <row r="5">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>110.429082</v>
+        <v>110.610402</v>
       </c>
     </row>
     <row r="6">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100.878</v>
+        <v>101.154</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>94.327716</v>
+        <v>94.478916</v>
       </c>
     </row>
     <row r="8">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>73.831</v>
+        <v>73.932</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.636387</v>
+        <v>72.76476</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>58.971087</v>
+        <v>59.091237</v>
       </c>
     </row>
     <row r="11">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50.7622644282</v>
+        <v>50.9011488726</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38.2279445340866</v>
+        <v>38.5894350883889</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32.94</v>
+        <v>32.985</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.2932564202</v>
+        <v>29.3739854036</v>
       </c>
     </row>
     <row r="15">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.184</v>
+        <v>23.232</v>
       </c>
     </row>
     <row r="16">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.184</v>
+        <v>23.232</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.3114791572</v>
+        <v>20.3461877682</v>
       </c>
     </row>
     <row r="18">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.72080108</v>
+        <v>19.74817827</v>
       </c>
     </row>
     <row r="19">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.2231967846</v>
+        <v>15.2579053956</v>
       </c>
     </row>
     <row r="20">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.0666511028347</v>
+        <v>15.0799399917235</v>
       </c>
     </row>
     <row r="21">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12.7110074296109</v>
+        <v>12.7242963184998</v>
       </c>
     </row>
     <row r="22">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.4427240143369</v>
+        <v>12.4889462365591</v>
       </c>
     </row>
     <row r="23">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12.427</v>
+        <v>12.461</v>
       </c>
     </row>
     <row r="24">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12.427</v>
+        <v>12.444</v>
       </c>
     </row>
     <row r="25">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12.427</v>
+        <v>12.444</v>
       </c>
     </row>
     <row r="26">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11.7826065242954</v>
+        <v>11.8014026176352</v>
       </c>
     </row>
     <row r="27">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.893909</v>
+        <v>10.935899</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>zion-wellington-rg-dev</t>
+          <t>zclassify-rg-dev</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10.1557395786</v>
+        <v>10.1765647452</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>zclassify-rg-dev</t>
+          <t>zion-reveal-rg-dev</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.1487978564</v>
+        <v>10.1765647452</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>zion-reveal-rg-dev</t>
+          <t>zion-wellington-rg-dev</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.1487978564</v>
+        <v>10.1765647452</v>
       </c>
     </row>
     <row r="31">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.999079992</v>
+        <v>10.0268552142</v>
       </c>
     </row>
     <row r="32">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="36">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6.353166</v>
+        <v>6.38559</v>
       </c>
     </row>
     <row r="37">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.282393166</v>
+        <v>5.2897263915</v>
       </c>
     </row>
     <row r="38">
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.0743989282</v>
+        <v>5.0882823726</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>niyati-zionaidemo</t>
+          <t>rg-demo-dev-eastus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.0743989282</v>
+        <v>5.0882823726</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rg-demo-dev-eastus</t>
+          <t>rg-medflow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.0743989282</v>
+        <v>5.0882823726</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rg-medflow</t>
+          <t>niyati-zionaidemo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.0743989282</v>
+        <v>5.0813406504</v>
       </c>
     </row>
     <row r="42">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.90379166666667</v>
+        <v>4.9105</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>zion-wellington-rg-dev</t>
+          <t>zion-reveal-rg-dev</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.90379166666667</v>
+        <v>4.9105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>zion-reveal-rg-dev</t>
+          <t>zion-wellington-rg-dev</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.89708333333334</v>
+        <v>4.9105</v>
       </c>
     </row>
     <row r="45">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.77992759856631</v>
+        <v>4.78657204301075</v>
       </c>
     </row>
     <row r="46">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.75034910394265</v>
+        <v>4.7569935483871</v>
       </c>
     </row>
     <row r="47">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.304905101</v>
+        <v>4.312173121</v>
       </c>
     </row>
     <row r="48">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.66</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="49">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.66</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="50">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.66</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="51">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.574046188005</v>
+        <v>3.580009084005</v>
       </c>
     </row>
     <row r="52">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.504651303</v>
+        <v>3.510342799</v>
       </c>
     </row>
     <row r="53">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.7378236178</v>
+        <v>1.74565674</v>
       </c>
     </row>
     <row r="54">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.140909</v>
+        <v>1.14249275</v>
       </c>
     </row>
     <row r="55">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.445749595947564</v>
+        <v>0.459039486832917</v>
       </c>
     </row>
     <row r="58">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.087470451305</v>
+        <v>0.087588285005</v>
       </c>
     </row>
     <row r="61">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.0342769835</v>
+        <v>0.0346667707</v>
       </c>
     </row>
     <row r="64">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.00624745</v>
+        <v>0.0062644</v>
       </c>
     </row>
     <row r="65">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.00624615</v>
+        <v>0.0062631</v>
       </c>
     </row>
     <row r="66">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.0061582</v>
+        <v>0.006175</v>
       </c>
     </row>
     <row r="67">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.002697175</v>
+        <v>0.0026984424</v>
       </c>
     </row>
     <row r="68">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.00180275</v>
+        <v>0.00181025</v>
       </c>
     </row>
     <row r="69">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.0011389158</v>
+        <v>0.0011402247</v>
       </c>
     </row>
     <row r="70">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.000972315</v>
+        <v>0.000974171</v>
       </c>
     </row>
     <row r="71">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.000599236</v>
+        <v>0.000599834</v>
       </c>
     </row>
     <row r="72">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.000430035</v>
+        <v>0.000431195</v>
       </c>
     </row>
     <row r="73">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.000359478</v>
+        <v>0.00035991</v>
       </c>
     </row>
     <row r="75">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.000320922</v>
+        <v>0.000321378</v>
       </c>
     </row>
     <row r="76">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.0002965836</v>
+        <v>0.0002975734</v>
       </c>
     </row>
     <row r="77">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7.92e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="87">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7.92e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="88">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>1530.446611829586</v>
+        <v>1533.859949650635</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>429.3228124334109</v>
+        <v>430.3858312954998</v>
       </c>
     </row>
     <row r="3">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>149.550980753</v>
+        <v>149.820009199</v>
       </c>
     </row>
     <row r="4">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136.5567996513397</v>
+        <v>136.8809149849285</v>
       </c>
     </row>
     <row r="5">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>130.5487989479476</v>
+        <v>130.7404220643329</v>
       </c>
     </row>
     <row r="6">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.0518114150939</v>
+        <v>125.2650477054939</v>
       </c>
     </row>
     <row r="7">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109.3803879230666</v>
+        <v>109.5660631452</v>
       </c>
     </row>
     <row r="8">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.9073227442</v>
+        <v>79.02221368860002</v>
       </c>
     </row>
     <row r="9">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.01696818973333</v>
+        <v>74.1783017452</v>
       </c>
     </row>
     <row r="10">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63.42237660319999</v>
+        <v>63.56626104759999</v>
       </c>
     </row>
     <row r="11">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.24734277538661</v>
+        <v>57.6914702390889</v>
       </c>
     </row>
     <row r="12">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.8234076042954</v>
+        <v>47.8795808876352</v>
       </c>
     </row>
     <row r="13">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.602697175</v>
+        <v>36.6526984424</v>
       </c>
     </row>
     <row r="14">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.7537873153369</v>
+        <v>16.8072943575591</v>
       </c>
     </row>
     <row r="15">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.01368244526667</v>
+        <v>16.0412167452</v>
       </c>
     </row>
     <row r="16">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.2236268196</v>
+        <v>15.2583365906</v>
       </c>
     </row>
     <row r="17">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.0423292158</v>
+        <v>13.0593305247</v>
       </c>
     </row>
     <row r="18">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.999079992</v>
+        <v>10.0268552142</v>
       </c>
     </row>
     <row r="19">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.233414928199999</v>
+        <v>5.240356650399999</v>
       </c>
     </row>
     <row r="20">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.0743989282</v>
+        <v>5.0882823726</v>
       </c>
     </row>
     <row r="21">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.77992759856631</v>
+        <v>4.78657204301075</v>
       </c>
     </row>
     <row r="22">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.75077950394265</v>
+        <v>4.7574239483871</v>
       </c>
     </row>
     <row r="23">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.140909</v>
+        <v>1.14249275</v>
       </c>
     </row>
     <row r="24">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.000972315</v>
+        <v>0.000974171</v>
       </c>
     </row>
     <row r="25">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.000849236</v>
+        <v>0.000849834</v>
       </c>
     </row>
     <row r="26">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.000359478</v>
+        <v>0.00035991</v>
       </c>
     </row>
     <row r="27">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.000320922</v>
+        <v>0.000321378</v>
       </c>
     </row>
     <row r="28">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7.92e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="32">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>485.431788</v>
+        <v>486.342255</v>
       </c>
     </row>
     <row r="3">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245.616</v>
+        <v>246.288</v>
       </c>
     </row>
     <row r="4">
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>178.0780314042</v>
+        <v>178.527621398</v>
       </c>
     </row>
     <row r="5">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121.160656186</v>
+        <v>121.326656186</v>
       </c>
     </row>
     <row r="6">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111.112</v>
+        <v>111.281</v>
       </c>
     </row>
     <row r="7">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.878</v>
+        <v>101.154</v>
       </c>
     </row>
     <row r="8">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>90.24054643570784</v>
+        <v>90.66873699001005</v>
       </c>
     </row>
     <row r="9">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.37016275000001</v>
+        <v>46.46617025</v>
       </c>
     </row>
     <row r="10">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.65728109021</v>
+        <v>37.71301495671</v>
       </c>
     </row>
     <row r="11">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.94</v>
+        <v>32.985</v>
       </c>
     </row>
     <row r="12">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.3</v>
+        <v>18.325</v>
       </c>
     </row>
     <row r="13">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.4427240143369</v>
+        <v>12.4889462365591</v>
       </c>
     </row>
     <row r="15">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.86075038888889</v>
+        <v>11.90274038888889</v>
       </c>
     </row>
     <row r="16">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11.7826065242954</v>
+        <v>11.8014026176352</v>
       </c>
     </row>
     <row r="17">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8.557163235947563</v>
+        <v>8.570453126832916</v>
       </c>
     </row>
     <row r="18">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0186518</v>
+        <v>0.0187025</v>
       </c>
     </row>
     <row r="19">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>425.542237806452</v>
+        <v>426.498569806452</v>
       </c>
     </row>
     <row r="4">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>245.616</v>
+        <v>246.288</v>
       </c>
     </row>
     <row r="5">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>212.28</v>
+        <v>212.57</v>
       </c>
     </row>
     <row r="6">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>140.147215104</v>
+        <v>140.339215104</v>
       </c>
     </row>
     <row r="7">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135.046920305</v>
+        <v>135.231920305</v>
       </c>
     </row>
     <row r="8">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>112.779212018935</v>
+        <v>113.028962018935</v>
       </c>
     </row>
     <row r="9">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>91.977902352</v>
+        <v>92.10390235200001</v>
       </c>
     </row>
     <row r="10">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.975804704</v>
+        <v>92.101804704</v>
       </c>
     </row>
     <row r="11">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="12">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.078401888</v>
+        <v>70.17440188800001</v>
       </c>
     </row>
     <row r="13">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>61.404</v>
+        <v>61.572</v>
       </c>
     </row>
     <row r="14">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41.9865645312</v>
+        <v>42.1017645312</v>
       </c>
     </row>
     <row r="15">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40.7976514</v>
+        <v>40.8541256</v>
       </c>
     </row>
     <row r="16">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32.9669472263055</v>
+        <v>33.0119472263055</v>
       </c>
     </row>
     <row r="17">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.0771111111111</v>
+        <v>25.2182222222222</v>
       </c>
     </row>
     <row r="18">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.49</v>
+        <v>23.526</v>
       </c>
     </row>
     <row r="19">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.392</v>
+        <v>23.424</v>
       </c>
     </row>
     <row r="20">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20.3036874282</v>
+        <v>20.3592378726</v>
       </c>
     </row>
     <row r="21">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.756359688</v>
+        <v>19.783791612</v>
       </c>
     </row>
     <row r="22">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19.72080108</v>
+        <v>19.74817827</v>
       </c>
     </row>
     <row r="23">
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19.6954301332</v>
+        <v>19.722808144</v>
       </c>
     </row>
     <row r="24">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.285</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="25">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14.7387875</v>
+        <v>14.75895</v>
       </c>
     </row>
     <row r="26">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.98</v>
+        <v>10.995</v>
       </c>
     </row>
     <row r="28">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10.198415913</v>
+        <v>10.226770959</v>
       </c>
     </row>
     <row r="29">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.1487978564</v>
+        <v>10.1765647452</v>
       </c>
     </row>
     <row r="30">
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.012328767123289</v>
+        <v>9.024657534246581</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zionadmin-rg</t>
+          <t>rg_1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.32</v>
+        <v>7.335</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rg_1</t>
+          <t>zionadmin-rg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.315</v>
+        <v>7.335</v>
       </c>
     </row>
     <row r="33">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.0743989282</v>
+        <v>5.0813406504</v>
       </c>
     </row>
     <row r="34">
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.66</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="36">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.66</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="37">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.96639784946237</v>
+        <v>1.96975806451613</v>
       </c>
     </row>
     <row r="41">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.83283165414581</v>
+        <v>1.8353376384894</v>
       </c>
     </row>
     <row r="42">
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.925496548040055</v>
+        <v>0.927265543779574</v>
       </c>
     </row>
     <row r="44">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.491935483870968</v>
+        <v>0.49260752688172</v>
       </c>
     </row>
     <row r="46">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.134916781</v>
+        <v>0.135306544</v>
       </c>
     </row>
     <row r="47">
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.080386184</v>
+        <v>0.0804292575</v>
       </c>
     </row>
     <row r="48">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.07335164719999999</v>
+        <v>0.0733518782</v>
       </c>
     </row>
     <row r="49">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0335951328091323</v>
+        <v>0.0336395524814725</v>
       </c>
     </row>
     <row r="50">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0156183415092528</v>
+        <v>0.0156624118983746</v>
       </c>
     </row>
     <row r="51">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0135069202</v>
+        <v>0.0135252898</v>
       </c>
     </row>
     <row r="52">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.00769183</v>
+        <v>0.007712854</v>
       </c>
     </row>
     <row r="53">
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.007616508</v>
+        <v>0.007627708</v>
       </c>
     </row>
     <row r="54">
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.00403105</v>
+        <v>0.00404215</v>
       </c>
     </row>
     <row r="56">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.002131498</v>
+        <v>0.0021321636</v>
       </c>
     </row>
     <row r="57">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.00152334140613675</v>
+        <v>0.00152457177639008</v>
       </c>
     </row>
     <row r="59">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.000683787467467785</v>
+        <v>0.000684613476085663</v>
       </c>
     </row>
     <row r="60">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.0003759392</v>
+        <v>0.0003761968</v>
       </c>
     </row>
     <row r="61">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.8376616537571e-05</v>
+        <v>2.83886305987835e-05</v>
       </c>
     </row>
     <row r="69">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2522.433008603189</v>
+        <v>2526.377061888525</v>
       </c>
     </row>
   </sheetData>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>574.4386675111722</v>
+        <v>575.6019168935948</v>
       </c>
     </row>
     <row r="3">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>505.4064320751299</v>
+        <v>506.5291711269923</v>
       </c>
     </row>
     <row r="4">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>330.4916716295093</v>
+        <v>330.9491898998984</v>
       </c>
     </row>
     <row r="6">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>195.9925179248165</v>
+        <v>196.3330729828306</v>
       </c>
     </row>
     <row r="7">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122.6781291254061</v>
+        <v>122.8515075457764</v>
       </c>
     </row>
     <row r="8">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.914128799935</v>
+        <v>113.164268562935</v>
       </c>
     </row>
     <row r="9">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.10015519999999</v>
+        <v>73.2001552</v>
       </c>
     </row>
     <row r="10">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.35697754031959</v>
+        <v>37.40702061381959</v>
       </c>
     </row>
     <row r="11">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25.0814831271111</v>
+        <v>25.2225942382222</v>
       </c>
     </row>
     <row r="12">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.3036874282</v>
+        <v>20.3592378726</v>
       </c>
     </row>
     <row r="13">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.746404008</v>
+        <v>14.766577708</v>
       </c>
     </row>
     <row r="14">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.1487978564</v>
+        <v>10.1765647452</v>
       </c>
     </row>
     <row r="15">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.15552348414581</v>
+        <v>9.178050492489399</v>
       </c>
     </row>
     <row r="16">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.025835687323289</v>
+        <v>9.038182824046581</v>
       </c>
     </row>
     <row r="17">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.076561388343045</v>
+        <v>5.083503368143044</v>
       </c>
     </row>
     <row r="19">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07335164719999999</v>
+        <v>0.0733518782</v>
       </c>
     </row>
     <row r="21">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00403105</v>
+        <v>0.00404215</v>
       </c>
     </row>
     <row r="22">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.002132558</v>
+        <v>0.0021332236</v>
       </c>
     </row>
     <row r="23">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>529.875734816</v>
+        <v>530.600734816</v>
       </c>
     </row>
     <row r="3">
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>440.281025306452</v>
+        <v>441.257519806452</v>
       </c>
     </row>
     <row r="5">
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>245.616</v>
+        <v>246.288</v>
       </c>
     </row>
     <row r="6">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212.28</v>
+        <v>212.57</v>
       </c>
     </row>
     <row r="7">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>167.0063287671233</v>
+        <v>167.3226575342466</v>
       </c>
     </row>
     <row r="8">
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115.5393267420639</v>
+        <v>115.793351722147</v>
       </c>
     </row>
     <row r="9">
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110.4973008378</v>
+        <v>110.6648128929</v>
       </c>
     </row>
     <row r="10">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62.2</v>
+        <v>62.315</v>
       </c>
     </row>
     <row r="11">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41.9865645312</v>
+        <v>42.1017645312</v>
       </c>
     </row>
     <row r="12">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35.5268842128</v>
+        <v>35.6171432682</v>
       </c>
     </row>
     <row r="13">
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.9669472263055</v>
+        <v>33.0119472263055</v>
       </c>
     </row>
     <row r="14">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.0771111111111</v>
+        <v>25.2182222222222</v>
       </c>
     </row>
     <row r="15">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.39220445</v>
+        <v>23.42420445</v>
       </c>
     </row>
     <row r="16">
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.458333333333338</v>
+        <v>2.46236559139785</v>
       </c>
     </row>
     <row r="19">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05160370682261942</v>
+        <v>0.05169426527701383</v>
       </c>
     </row>
     <row r="21">
